--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D492"/>
+  <dimension ref="A1:D493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8942,6 +8942,26 @@
         <v>4</v>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D493"/>
+  <dimension ref="A1:D494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8953,12 +8953,26 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C493" t="inlineStr"/>
       <c r="D493" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>substance active</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>87</v>
+      </c>
+      <c r="D494" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D494"/>
+  <dimension ref="A1:D495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8976,6 +8976,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D495"/>
+  <dimension ref="A1:D497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8987,12 +8987,44 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C495" t="inlineStr"/>
       <c r="D495" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>122</v>
+      </c>
+      <c r="D496" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>122</v>
+      </c>
+      <c r="D497" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D497"/>
+  <dimension ref="A1:D498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9028,6 +9028,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D498"/>
+  <dimension ref="A1:D499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9039,12 +9039,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr">
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D498" t="n">
+      <c r="D499" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D499"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9055,12 +9055,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C499" t="inlineStr">
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D499" t="n">
+      <c r="D500" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9071,13 +9071,63 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C500" t="inlineStr"/>
       <c r="D500" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>128</v>
+      </c>
+      <c r="D501" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>129</v>
+      </c>
+      <c r="D502" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>130</v>
+      </c>
+      <c r="D503" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D503"/>
+  <dimension ref="A1:D505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9130,6 +9130,42 @@
         <v>3</v>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>6</v>
+      </c>
+      <c r="D504" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>6</v>
+      </c>
+      <c r="D505" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D505"/>
+  <dimension ref="A1:D507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9166,6 +9166,42 @@
         <v>1</v>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>distribution/conseil</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>49</v>
+      </c>
+      <c r="D506" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>49</v>
+      </c>
+      <c r="D507" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D507"/>
+  <dimension ref="A1:D508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9202,6 +9202,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D508"/>
+  <dimension ref="A1:D520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9213,13 +9213,225 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C508" t="inlineStr"/>
       <c r="D508" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>7</v>
+      </c>
+      <c r="D509" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>44</v>
+      </c>
+      <c r="D510" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>122</v>
+      </c>
+      <c r="D511" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>126</v>
+      </c>
+      <c r="D512" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>126</v>
+      </c>
+      <c r="D513" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>134</v>
+      </c>
+      <c r="D514" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>138</v>
+      </c>
+      <c r="D515" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>138</v>
+      </c>
+      <c r="D516" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>145</v>
+      </c>
+      <c r="D517" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>149</v>
+      </c>
+      <c r="D518" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>150</v>
+      </c>
+      <c r="D519" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>165</v>
+      </c>
+      <c r="D520" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D520"/>
+  <dimension ref="A1:D521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9434,6 +9434,26 @@
         <v>2</v>
       </c>
     </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D521"/>
+  <dimension ref="A1:D523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9445,12 +9445,44 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C521" t="inlineStr"/>
       <c r="D521" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>espèces exotiques envahissantes</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>67</v>
+      </c>
+      <c r="D522" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>92</v>
+      </c>
+      <c r="D523" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D523"/>
+  <dimension ref="A1:D524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9486,6 +9486,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D524"/>
+  <dimension ref="A1:D525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9497,12 +9497,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C524" t="inlineStr">
+      <c r="C524" t="inlineStr"/>
+      <c r="D524" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D524" t="n">
+      <c r="D525" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D525"/>
+  <dimension ref="A1:D526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9513,12 +9513,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C525" t="inlineStr">
+      <c r="C525" t="inlineStr"/>
+      <c r="D525" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D525" t="n">
+      <c r="D526" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D526"/>
+  <dimension ref="A1:D531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9529,12 +9529,98 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C526" t="inlineStr"/>
       <c r="D526" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>83</v>
+      </c>
+      <c r="D527" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>84</v>
+      </c>
+      <c r="D528" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>84</v>
+      </c>
+      <c r="D529" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>96</v>
+      </c>
+      <c r="D530" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>114</v>
+      </c>
+      <c r="D531" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D531"/>
+  <dimension ref="A1:D538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9624,6 +9624,132 @@
         <v>1</v>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>conditionnalité</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>2</v>
+      </c>
+      <c r="D532" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>conditionnalité</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>44</v>
+      </c>
+      <c r="D533" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>conditionnalité</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>46</v>
+      </c>
+      <c r="D534" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>conditionnalité</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>48</v>
+      </c>
+      <c r="D535" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>50</v>
+      </c>
+      <c r="D536" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>conditionnalité</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>50</v>
+      </c>
+      <c r="D537" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>espèces exotiques envahissantes</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>80</v>
+      </c>
+      <c r="D538" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D538"/>
+  <dimension ref="A1:D554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9750,6 +9750,294 @@
         <v>1</v>
       </c>
     </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>distribution/conseil</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>50</v>
+      </c>
+      <c r="D539" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>50</v>
+      </c>
+      <c r="D540" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>phytolicence</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>53</v>
+      </c>
+      <c r="D541" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>assistant usage professionnel</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>53</v>
+      </c>
+      <c r="D542" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>53</v>
+      </c>
+      <c r="D543" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>phytolicence</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>54</v>
+      </c>
+      <c r="D544" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>assistant usage professionnel</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>54</v>
+      </c>
+      <c r="D545" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>54</v>
+      </c>
+      <c r="D546" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>phytolicence</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>55</v>
+      </c>
+      <c r="D547" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>assistant usage professionnel</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>55</v>
+      </c>
+      <c r="D548" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>55</v>
+      </c>
+      <c r="D549" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>phytolicence</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>56</v>
+      </c>
+      <c r="D550" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>assistant usage professionnel</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>56</v>
+      </c>
+      <c r="D551" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>56</v>
+      </c>
+      <c r="D552" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>espèces exotiques envahissantes</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>155</v>
+      </c>
+      <c r="D553" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>espèces exotiques envahissantes</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>157</v>
+      </c>
+      <c r="D554" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D554"/>
+  <dimension ref="A1:D555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10038,6 +10038,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D555"/>
+  <dimension ref="A1:D557"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10049,12 +10049,44 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C555" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C555" t="inlineStr"/>
       <c r="D555" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>220</v>
+      </c>
+      <c r="D556" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>224</v>
+      </c>
+      <c r="D557" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D557"/>
+  <dimension ref="A1:D558"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10090,6 +10090,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D558"/>
+  <dimension ref="A1:D567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10101,12 +10101,170 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C558" t="inlineStr"/>
       <c r="D558" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>27</v>
+      </c>
+      <c r="D559" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>espèces exotiques envahissantes</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>28</v>
+      </c>
+      <c r="D560" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>30</v>
+      </c>
+      <c r="D561" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>zone tampon</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>33</v>
+      </c>
+      <c r="D562" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>37</v>
+      </c>
+      <c r="D563" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>37</v>
+      </c>
+      <c r="D564" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>37</v>
+      </c>
+      <c r="D565" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>espèces exotiques envahissantes</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>38</v>
+      </c>
+      <c r="D566" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>38</v>
+      </c>
+      <c r="D567" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D567"/>
+  <dimension ref="A1:D572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10268,6 +10268,96 @@
         <v>1</v>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>feu bactérien</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>2</v>
+      </c>
+      <c r="D568" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>feu bactérien</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>21</v>
+      </c>
+      <c r="D569" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>zone tampon</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>21</v>
+      </c>
+      <c r="D570" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>feu bactérien</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>25</v>
+      </c>
+      <c r="D571" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>feu bactérien</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>29</v>
+      </c>
+      <c r="D572" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D572"/>
+  <dimension ref="A1:D573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10358,6 +10358,24 @@
         <v>1</v>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>219</v>
+      </c>
+      <c r="D573" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D573"/>
+  <dimension ref="A1:D584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10376,6 +10376,204 @@
         <v>1</v>
       </c>
     </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>26</v>
+      </c>
+      <c r="D574" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>27</v>
+      </c>
+      <c r="D575" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>28</v>
+      </c>
+      <c r="D576" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>28</v>
+      </c>
+      <c r="D577" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>29</v>
+      </c>
+      <c r="D578" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>30</v>
+      </c>
+      <c r="D579" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>31</v>
+      </c>
+      <c r="D580" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>33</v>
+      </c>
+      <c r="D581" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>33</v>
+      </c>
+      <c r="D582" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>33</v>
+      </c>
+      <c r="D583" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>34</v>
+      </c>
+      <c r="D584" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D584"/>
+  <dimension ref="A1:D587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10574,6 +10574,60 @@
         <v>1</v>
       </c>
     </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>28</v>
+      </c>
+      <c r="D585" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>53</v>
+      </c>
+      <c r="D586" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>53</v>
+      </c>
+      <c r="D587" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D587"/>
+  <dimension ref="A1:D588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10628,6 +10628,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D588"/>
+  <dimension ref="A1:D589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10639,12 +10639,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C588" t="inlineStr">
+      <c r="C588" t="inlineStr"/>
+      <c r="D588" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D588" t="n">
+      <c r="D589" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D589"/>
+  <dimension ref="A1:D590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10655,12 +10655,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C589" t="inlineStr">
+      <c r="C589" t="inlineStr"/>
+      <c r="D589" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D589" t="n">
+      <c r="D590" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D590"/>
+  <dimension ref="A1:D591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10671,12 +10671,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C590" t="inlineStr">
+      <c r="C590" t="inlineStr"/>
+      <c r="D590" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D590" t="n">
+      <c r="D591" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D591"/>
+  <dimension ref="A1:D593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10687,13 +10687,45 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C591" t="inlineStr"/>
       <c r="D591" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>142</v>
+      </c>
+      <c r="D592" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>143</v>
+      </c>
+      <c r="D593" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D593"/>
+  <dimension ref="A1:D600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10728,6 +10728,132 @@
         <v>3</v>
       </c>
     </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>78</v>
+      </c>
+      <c r="D594" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>80</v>
+      </c>
+      <c r="D595" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>85</v>
+      </c>
+      <c r="D596" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>85</v>
+      </c>
+      <c r="D597" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>86</v>
+      </c>
+      <c r="D598" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>espèces exotiques envahissantes</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>89</v>
+      </c>
+      <c r="D599" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>89</v>
+      </c>
+      <c r="D600" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D600"/>
+  <dimension ref="A1:D604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10854,6 +10854,78 @@
         <v>2</v>
       </c>
     </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>réduction de la dérive</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>95</v>
+      </c>
+      <c r="D601" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>herbicides</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>141</v>
+      </c>
+      <c r="D602" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>herbicides</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>142</v>
+      </c>
+      <c r="D603" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>181</v>
+      </c>
+      <c r="D604" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D604"/>
+  <dimension ref="A1:D605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10926,6 +10926,24 @@
         <v>1</v>
       </c>
     </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>zone tampon</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>46</v>
+      </c>
+      <c r="D605" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D605"/>
+  <dimension ref="A1:D606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10944,6 +10944,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D606"/>
+  <dimension ref="A1:D607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10955,12 +10955,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C606" t="inlineStr">
+      <c r="C606" t="inlineStr"/>
+      <c r="D606" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D606" t="n">
+      <c r="D607" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D607"/>
+  <dimension ref="A1:D608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10971,12 +10971,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C607" t="inlineStr">
+      <c r="C607" t="inlineStr"/>
+      <c r="D607" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D607" t="n">
+      <c r="D608" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D608"/>
+  <dimension ref="A1:D609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10987,12 +10987,26 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C608" t="inlineStr"/>
       <c r="D608" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>substance active</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>252</v>
+      </c>
+      <c r="D609" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D609"/>
+  <dimension ref="A1:D611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11010,6 +11010,42 @@
         <v>1</v>
       </c>
     </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>75</v>
+      </c>
+      <c r="D610" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>phytolicence</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>81</v>
+      </c>
+      <c r="D611" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D611"/>
+  <dimension ref="A1:D612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11046,6 +11046,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D612"/>
+  <dimension ref="A1:D613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11057,12 +11057,26 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C612" t="inlineStr"/>
       <c r="D612" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>19</v>
+      </c>
+      <c r="D613" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D613"/>
+  <dimension ref="A1:D616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11080,6 +11080,60 @@
         <v>1</v>
       </c>
     </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>32</v>
+      </c>
+      <c r="D614" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>68</v>
+      </c>
+      <c r="D615" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>116</v>
+      </c>
+      <c r="D616" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D616"/>
+  <dimension ref="A1:D617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11134,6 +11134,26 @@
         <v>7</v>
       </c>
     </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D617"/>
+  <dimension ref="A1:D618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11145,12 +11145,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C617" t="inlineStr">
+      <c r="C617" t="inlineStr"/>
+      <c r="D617" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D617" t="n">
+      <c r="D618" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D618"/>
+  <dimension ref="A1:D626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11161,13 +11161,153 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C618" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C618" t="inlineStr"/>
       <c r="D618" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>3</v>
+      </c>
+      <c r="D619" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>46</v>
+      </c>
+      <c r="D620" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>46</v>
+      </c>
+      <c r="D621" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>réduction de la dérive</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>46</v>
+      </c>
+      <c r="D622" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>47</v>
+      </c>
+      <c r="D623" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>zone tampon</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>47</v>
+      </c>
+      <c r="D624" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>réduction de la dérive</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>47</v>
+      </c>
+      <c r="D625" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>48</v>
+      </c>
+      <c r="D626" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D626"/>
+  <dimension ref="A1:D627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11310,6 +11310,24 @@
         <v>3</v>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>201</v>
+      </c>
+      <c r="D627" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D627"/>
+  <dimension ref="A1:D628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11328,6 +11328,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D628"/>
+  <dimension ref="A1:D629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11339,12 +11339,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C628" t="inlineStr">
+      <c r="C628" t="inlineStr"/>
+      <c r="D628" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D628" t="n">
+      <c r="D629" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D629"/>
+  <dimension ref="A1:D630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11355,12 +11355,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C629" t="inlineStr">
+      <c r="C629" t="inlineStr"/>
+      <c r="D629" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D629" t="n">
+      <c r="D630" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D630"/>
+  <dimension ref="A1:D652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11371,13 +11371,405 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C630" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C630" t="inlineStr"/>
       <c r="D630" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>16</v>
+      </c>
+      <c r="D631" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>32</v>
+      </c>
+      <c r="D632" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>réduction de la dérive</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>32</v>
+      </c>
+      <c r="D633" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>33</v>
+      </c>
+      <c r="D634" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>réduction de la dérive</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>33</v>
+      </c>
+      <c r="D635" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>34</v>
+      </c>
+      <c r="D636" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>réduction de la dérive</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>34</v>
+      </c>
+      <c r="D637" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>35</v>
+      </c>
+      <c r="D638" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>36</v>
+      </c>
+      <c r="D639" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>39</v>
+      </c>
+      <c r="D640" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>41</v>
+      </c>
+      <c r="D641" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>42</v>
+      </c>
+      <c r="D642" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>43</v>
+      </c>
+      <c r="D643" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>45</v>
+      </c>
+      <c r="D644" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>57</v>
+      </c>
+      <c r="D645" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>58</v>
+      </c>
+      <c r="D646" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>59</v>
+      </c>
+      <c r="D647" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>60</v>
+      </c>
+      <c r="D648" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>61</v>
+      </c>
+      <c r="D649" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>62</v>
+      </c>
+      <c r="D650" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>63</v>
+      </c>
+      <c r="D651" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>64</v>
+      </c>
+      <c r="D652" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D652"/>
+  <dimension ref="A1:D653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11772,6 +11772,26 @@
         <v>3</v>
       </c>
     </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D653"/>
+  <dimension ref="A1:D654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11783,12 +11783,26 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C653" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C653" t="inlineStr"/>
       <c r="D653" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>25</v>
+      </c>
+      <c r="D654" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D654"/>
+  <dimension ref="A1:D655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11806,6 +11806,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D655"/>
+  <dimension ref="A1:D660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11817,13 +11817,99 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C655" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C655" t="inlineStr"/>
       <c r="D655" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>34</v>
+      </c>
+      <c r="D656" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>40</v>
+      </c>
+      <c r="D657" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>46</v>
+      </c>
+      <c r="D658" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>conditionnalité</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>78</v>
+      </c>
+      <c r="D659" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>agriculture biologique</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>78</v>
+      </c>
+      <c r="D660" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D660"/>
+  <dimension ref="A1:D662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11912,6 +11912,42 @@
         <v>3</v>
       </c>
     </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>59</v>
+      </c>
+      <c r="D661" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>62</v>
+      </c>
+      <c r="D662" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D662"/>
+  <dimension ref="A1:D664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11948,6 +11948,42 @@
         <v>1</v>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>44</v>
+      </c>
+      <c r="D663" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>45</v>
+      </c>
+      <c r="D664" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D664"/>
+  <dimension ref="A1:D666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11984,6 +11984,42 @@
         <v>1</v>
       </c>
     </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>99</v>
+      </c>
+      <c r="D665" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>103</v>
+      </c>
+      <c r="D666" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D666"/>
+  <dimension ref="A1:D667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12020,6 +12020,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D667"/>
+  <dimension ref="A1:D672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12031,12 +12031,98 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C667" t="inlineStr"/>
       <c r="D667" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>270</v>
+      </c>
+      <c r="D668" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>271</v>
+      </c>
+      <c r="D669" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>272</v>
+      </c>
+      <c r="D670" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>272</v>
+      </c>
+      <c r="D671" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>273</v>
+      </c>
+      <c r="D672" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D672"/>
+  <dimension ref="A1:D673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12126,6 +12126,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D673"/>
+  <dimension ref="A1:D674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12137,12 +12137,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C673" t="inlineStr">
+      <c r="C673" t="inlineStr"/>
+      <c r="D673" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D673" t="n">
+      <c r="D674" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D674"/>
+  <dimension ref="A1:D676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12153,13 +12153,45 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C674" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C674" t="inlineStr"/>
       <c r="D674" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>66</v>
+      </c>
+      <c r="D675" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>81</v>
+      </c>
+      <c r="D676" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D676"/>
+  <dimension ref="A1:D677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12194,6 +12194,24 @@
         <v>2</v>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>buse</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>145</v>
+      </c>
+      <c r="D677" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D677"/>
+  <dimension ref="A1:D683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12212,6 +12212,114 @@
         <v>2</v>
       </c>
     </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>lutte intégrée</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>6</v>
+      </c>
+      <c r="D678" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>substance active</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>39</v>
+      </c>
+      <c r="D679" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>lutte intégrée</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>104</v>
+      </c>
+      <c r="D680" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>138</v>
+      </c>
+      <c r="D681" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>141</v>
+      </c>
+      <c r="D682" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>144</v>
+      </c>
+      <c r="D683" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D683"/>
+  <dimension ref="A1:D685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12320,6 +12320,42 @@
         <v>1</v>
       </c>
     </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>8</v>
+      </c>
+      <c r="D684" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>233</v>
+      </c>
+      <c r="D685" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D685"/>
+  <dimension ref="A1:D686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12356,6 +12356,26 @@
         <v>10</v>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D686"/>
+  <dimension ref="A1:D687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12367,12 +12367,26 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C686" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C686" t="inlineStr"/>
       <c r="D686" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>16</v>
+      </c>
+      <c r="D687" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D687"/>
+  <dimension ref="A1:D688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12390,6 +12390,24 @@
         <v>1</v>
       </c>
     </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>substance active</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>57</v>
+      </c>
+      <c r="D688" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D688"/>
+  <dimension ref="A1:D689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12408,6 +12408,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D689"/>
+  <dimension ref="A1:D692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12419,13 +12419,63 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C689" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C689" t="inlineStr"/>
       <c r="D689" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>substance active</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>38</v>
+      </c>
+      <c r="D690" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>phytolicence</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>38</v>
+      </c>
+      <c r="D691" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>distribution/conseil</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>38</v>
+      </c>
+      <c r="D692" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D692"/>
+  <dimension ref="A1:D694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12478,6 +12478,42 @@
         <v>2</v>
       </c>
     </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>organismes de quarantaine</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>228</v>
+      </c>
+      <c r="D693" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>organismes de quarantaine</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>232</v>
+      </c>
+      <c r="D694" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D694"/>
+  <dimension ref="A1:D698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12514,6 +12514,78 @@
         <v>1</v>
       </c>
     </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>83</v>
+      </c>
+      <c r="D695" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>85</v>
+      </c>
+      <c r="D696" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>87</v>
+      </c>
+      <c r="D697" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>88</v>
+      </c>
+      <c r="D698" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D698"/>
+  <dimension ref="A1:D699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12586,6 +12586,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D699"/>
+  <dimension ref="A1:D700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12597,12 +12597,26 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C699" t="inlineStr"/>
       <c r="D699" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>20</v>
+      </c>
+      <c r="D700" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D700"/>
+  <dimension ref="A1:D701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12620,6 +12620,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D701"/>
+  <dimension ref="A1:D702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12631,12 +12631,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C701" t="inlineStr">
+      <c r="C701" t="inlineStr"/>
+      <c r="D701" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D701" t="n">
+      <c r="D702" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D702"/>
+  <dimension ref="A1:D709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12647,13 +12647,135 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C702" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C702" t="inlineStr"/>
       <c r="D702" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>51</v>
+      </c>
+      <c r="D703" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>61</v>
+      </c>
+      <c r="D704" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>62</v>
+      </c>
+      <c r="D705" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>63</v>
+      </c>
+      <c r="D706" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>63</v>
+      </c>
+      <c r="D707" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>substance active</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>191</v>
+      </c>
+      <c r="D708" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>261</v>
+      </c>
+      <c r="D709" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D709"/>
+  <dimension ref="A1:D710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12778,6 +12778,24 @@
         <v>4</v>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>167</v>
+      </c>
+      <c r="D710" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D710"/>
+  <dimension ref="A1:D711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12796,6 +12796,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D711"/>
+  <dimension ref="A1:D712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12807,12 +12807,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr">
+      <c r="C711" t="inlineStr"/>
+      <c r="D711" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D711" t="n">
+      <c r="D712" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D712"/>
+  <dimension ref="A1:D713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12823,12 +12823,28 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr">
+      <c r="C712" t="inlineStr"/>
+      <c r="D712" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="D712" t="n">
+      <c r="D713" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D713"/>
+  <dimension ref="A1:D714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12839,12 +12839,26 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C713" t="inlineStr"/>
       <c r="D713" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>40</v>
+      </c>
+      <c r="D714" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D714"/>
+  <dimension ref="A1:D715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12862,6 +12862,24 @@
         <v>1</v>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>85</v>
+      </c>
+      <c r="D715" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D715"/>
+  <dimension ref="A1:D716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12880,6 +12880,26 @@
         <v>2</v>
       </c>
     </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D716"/>
+  <dimension ref="A1:D718"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12891,13 +12891,45 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C716" t="inlineStr"/>
       <c r="D716" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>95</v>
+      </c>
+      <c r="D717" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>95</v>
+      </c>
+      <c r="D718" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D718"/>
+  <dimension ref="A1:D722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12932,6 +12932,78 @@
         <v>2</v>
       </c>
     </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>3</v>
+      </c>
+      <c r="D719" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>64</v>
+      </c>
+      <c r="D720" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>72</v>
+      </c>
+      <c r="D721" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>73</v>
+      </c>
+      <c r="D722" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D722"/>
+  <dimension ref="A1:D723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13004,6 +13004,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D723"/>
+  <dimension ref="A1:D725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13015,13 +13015,45 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C723" t="inlineStr"/>
       <c r="D723" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>95</v>
+      </c>
+      <c r="D724" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>181</v>
+      </c>
+      <c r="D725" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D725"/>
+  <dimension ref="A1:D735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13056,6 +13056,186 @@
         <v>2</v>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>15</v>
+      </c>
+      <c r="D726" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>lutte intégrée</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>16</v>
+      </c>
+      <c r="D727" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>substances actives</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>17</v>
+      </c>
+      <c r="D728" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>lutte intégrée</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>17</v>
+      </c>
+      <c r="D729" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>substances actives</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>18</v>
+      </c>
+      <c r="D730" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>lutte intégrée</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>18</v>
+      </c>
+      <c r="D731" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>lutte intégrée</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>20</v>
+      </c>
+      <c r="D732" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>21</v>
+      </c>
+      <c r="D733" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>54</v>
+      </c>
+      <c r="D734" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>agriculture biologique</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>59</v>
+      </c>
+      <c r="D735" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D735"/>
+  <dimension ref="A1:D737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13236,6 +13236,42 @@
         <v>1</v>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>organismes de quarantaine</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>3</v>
+      </c>
+      <c r="D736" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>organismes de quarantaine</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>68</v>
+      </c>
+      <c r="D737" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D737"/>
+  <dimension ref="A1:D738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13272,6 +13272,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D738"/>
+  <dimension ref="A1:D743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13283,12 +13283,98 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C738" t="inlineStr"/>
       <c r="D738" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>67</v>
+      </c>
+      <c r="D739" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>68</v>
+      </c>
+      <c r="D740" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>ruissellement</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>70</v>
+      </c>
+      <c r="D741" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>eaux souterraines</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>71</v>
+      </c>
+      <c r="D742" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>71</v>
+      </c>
+      <c r="D743" t="n">
         <v>1</v>
       </c>
     </row>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D743"/>
+  <dimension ref="A1:D744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13378,6 +13378,24 @@
         <v>1</v>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>bonnes pratiques</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>76</v>
+      </c>
+      <c r="D744" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D744"/>
+  <dimension ref="A1:D745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13396,6 +13396,24 @@
         <v>1</v>
       </c>
     </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>eaux de surface</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>118</v>
+      </c>
+      <c r="D745" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D745"/>
+  <dimension ref="A1:D746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13414,6 +13414,26 @@
         <v>2</v>
       </c>
     </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Rien ne nous concerne aujourd'hui !</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/result/Data.xlsx
+++ b/result/Data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D746"/>
+  <dimension ref="A1:D747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13425,12 +13425,26 @@
           <t>Rien ne nous concerne aujourd'hui !</t>
         </is>
       </c>
-      <c r="C746" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
+      <c r="C746" t="inlineStr"/>
       <c r="D746" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>développement durable</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>359</v>
+      </c>
+      <c r="D747" t="n">
         <v>1</v>
       </c>
     </row>
